--- a/database/event/4281/event_4281_evp_summary.xlsx
+++ b/database/event/4281/event_4281_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.9296</v>
+        <v>10.8931</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1256</v>
+        <v>6.1051</v>
       </c>
       <c r="D2" t="n">
-        <v>3.994</v>
+        <v>3.8959</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9296</v>
+        <v>10.8931</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7452</v>
+        <v>4.7086</v>
       </c>
       <c r="G2" t="n">
         <v>6.1845</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1373</v>
+        <v>5.0801</v>
       </c>
       <c r="I2" t="n">
         <v>5.2094</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8694</v>
+        <v>7.9054</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4105</v>
+        <v>4.4306</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7577</v>
+        <v>2.7056</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8694</v>
+        <v>7.9054</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4504</v>
+        <v>4.4864</v>
       </c>
       <c r="G3" t="n">
         <v>3.419</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3445</v>
+        <v>5.4895</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3318</v>
+        <v>4.4494</v>
       </c>
       <c r="J3" t="n">
         <v>3.419</v>
@@ -575,7 +575,7 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7508</v>
+        <v>7.868399999999999</v>
       </c>
       <c r="N3" t="n">
         <v>359</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3019</v>
+        <v>6.5668</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5319</v>
+        <v>3.6804</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1245</v>
+        <v>2.1723</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3019</v>
+        <v>6.5668</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4021</v>
+        <v>4.667</v>
       </c>
       <c r="G4" t="n">
         <v>1.8998</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5994</v>
+        <v>5.0148</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6639</v>
+        <v>5.1425</v>
       </c>
       <c r="J4" t="n">
         <v>1.8998</v>
@@ -621,7 +621,7 @@
         <v>109</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5637</v>
+        <v>7.0423</v>
       </c>
       <c r="N4" t="n">
         <v>382</v>
@@ -640,7 +640,7 @@
         <v>3.2515</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9224</v>
+        <v>1.8674</v>
       </c>
       <c r="E5" t="n">
         <v>5.8016</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0773</v>
+        <v>5.1448</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8456</v>
+        <v>2.8834</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6298</v>
+        <v>1.6058</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0773</v>
+        <v>5.1448</v>
       </c>
       <c r="F6" t="n">
-        <v>4.357</v>
+        <v>4.4245</v>
       </c>
       <c r="G6" t="n">
         <v>0.7203000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9689</v>
+        <v>5.2405</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0274</v>
+        <v>4.2476</v>
       </c>
       <c r="J6" t="n">
         <v>0.7203000000000001</v>
@@ -713,7 +713,7 @@
         <v>90</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7477</v>
+        <v>4.9679</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -732,7 +732,7 @@
         <v>2.7674</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5734</v>
+        <v>1.5233</v>
       </c>
       <c r="E7" t="n">
         <v>4.9378</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9314</v>
+        <v>4.8868</v>
       </c>
       <c r="C8" t="n">
-        <v>2.7638</v>
+        <v>2.7388</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5708</v>
+        <v>1.503</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9314</v>
+        <v>4.8868</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0013</v>
+        <v>3.9567</v>
       </c>
       <c r="G8" t="n">
         <v>0.9301</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0013</v>
+        <v>3.9567</v>
       </c>
       <c r="I8" t="n">
         <v>4.0574</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2452</v>
+        <v>4.2553</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3793</v>
+        <v>2.3849</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2936</v>
+        <v>1.2514</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2452</v>
+        <v>4.2553</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4191</v>
+        <v>4.4292</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1739</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2188</v>
+        <v>5.2591</v>
       </c>
       <c r="I9" t="n">
-        <v>4.23</v>
+        <v>4.2627</v>
       </c>
       <c r="J9" t="n">
         <v>-0.1739</v>
@@ -851,7 +851,7 @@
         <v>90</v>
       </c>
       <c r="M9" t="n">
-        <v>4.056100000000001</v>
+        <v>4.0888</v>
       </c>
       <c r="N9" t="n">
         <v>208</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9521</v>
+        <v>4.0736</v>
       </c>
       <c r="C10" t="n">
-        <v>2.215</v>
+        <v>2.2831</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1752</v>
+        <v>1.179</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9521</v>
+        <v>4.0736</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3102</v>
+        <v>4.4317</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3581</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7803</v>
+        <v>5.2692</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8745</v>
+        <v>4.2709</v>
       </c>
       <c r="J10" t="n">
         <v>-0.3581</v>
@@ -897,7 +897,7 @@
         <v>90</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5164</v>
+        <v>3.9128</v>
       </c>
       <c r="N10" t="n">
         <v>208</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6598</v>
+        <v>3.7356</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0512</v>
+        <v>2.0936</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0571</v>
+        <v>1.0444</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6598</v>
+        <v>3.7356</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6472</v>
+        <v>2.1036</v>
       </c>
       <c r="G11" t="n">
-        <v>4.307</v>
+        <v>1.632</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6472</v>
+        <v>2.1036</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5246</v>
+        <v>1.705</v>
       </c>
       <c r="J11" t="n">
-        <v>4.307</v>
+        <v>1.632</v>
       </c>
       <c r="K11" t="n">
         <v>195</v>
@@ -943,7 +943,7 @@
         <v>164</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7824</v>
+        <v>3.337</v>
       </c>
       <c r="N11" t="n">
         <v>359</v>
@@ -952,170 +952,170 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.566</v>
+        <v>3.7232</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9986</v>
+        <v>2.0867</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0192</v>
+        <v>1.0394</v>
       </c>
       <c r="E12" t="n">
-        <v>3.566</v>
+        <v>3.7232</v>
       </c>
       <c r="F12" t="n">
-        <v>1.934</v>
+        <v>4.2026</v>
       </c>
       <c r="G12" t="n">
-        <v>1.632</v>
+        <v>-0.4794</v>
       </c>
       <c r="H12" t="n">
-        <v>1.934</v>
+        <v>4.3474</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5676</v>
+        <v>3.5237</v>
       </c>
       <c r="J12" t="n">
-        <v>1.632</v>
+        <v>-0.4794</v>
       </c>
       <c r="K12" t="n">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="L12" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1996</v>
+        <v>3.0443</v>
       </c>
       <c r="N12" t="n">
-        <v>359</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5163</v>
+        <v>3.6598</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9707</v>
+        <v>2.0512</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9991</v>
+        <v>1.0142</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5163</v>
+        <v>3.6598</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9957</v>
+        <v>-0.6472</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4794</v>
+        <v>4.307</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9957</v>
+        <v>-0.6472</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2386</v>
+        <v>-0.5246</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4794</v>
+        <v>4.307</v>
       </c>
       <c r="K13" t="n">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="L13" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7592</v>
+        <v>3.7824</v>
       </c>
       <c r="N13" t="n">
-        <v>208</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1489</v>
+        <v>3.4429</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7648</v>
+        <v>1.9296</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8507</v>
+        <v>0.9277</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1489</v>
+        <v>3.4429</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1489</v>
+        <v>3.4429</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1489</v>
+        <v>3.4429</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1782</v>
+        <v>3.4429</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1782</v>
+        <v>3.4429</v>
       </c>
       <c r="N14" t="n">
-        <v>224</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9261</v>
+        <v>3.1254</v>
       </c>
       <c r="C15" t="n">
-        <v>1.64</v>
+        <v>1.7517</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7607</v>
+        <v>0.8012</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9261</v>
+        <v>3.1254</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9261</v>
+        <v>3.1254</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9261</v>
+        <v>3.1254</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9534</v>
+        <v>3.1782</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9534</v>
+        <v>3.1782</v>
       </c>
       <c r="N15" t="n">
         <v>224</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9036</v>
+        <v>3.0753</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6273</v>
+        <v>1.7236</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7516</v>
+        <v>0.7813</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9036</v>
+        <v>3.0753</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9036</v>
+        <v>2.7199</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3554</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9036</v>
+        <v>2.7199</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9307</v>
+        <v>2.7199</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3554</v>
       </c>
       <c r="K16" t="n">
-        <v>224</v>
+        <v>148</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9307</v>
+        <v>3.0753</v>
       </c>
       <c r="N16" t="n">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7352</v>
+        <v>2.9043</v>
       </c>
       <c r="C17" t="n">
-        <v>1.533</v>
+        <v>1.6277</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6836</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7352</v>
+        <v>2.9043</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3798</v>
+        <v>2.9043</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3554</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3798</v>
+        <v>2.9043</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3798</v>
+        <v>2.9534</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3554</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7352</v>
+        <v>2.9534</v>
       </c>
       <c r="N17" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6068</v>
+        <v>2.882</v>
       </c>
       <c r="C18" t="n">
-        <v>1.461</v>
+        <v>1.6152</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6317</v>
+        <v>0.7043</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6068</v>
+        <v>2.882</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6068</v>
+        <v>2.882</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6068</v>
+        <v>2.882</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6068</v>
+        <v>2.9307</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6068</v>
+        <v>2.9307</v>
       </c>
       <c r="N18" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>1.446</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6209</v>
+        <v>0.584</v>
       </c>
       <c r="E19" t="n">
         <v>2.5801</v>
@@ -1330,7 +1330,7 @@
         <v>1.3616</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5601</v>
+        <v>0.524</v>
       </c>
       <c r="E20" t="n">
         <v>2.4294</v>
@@ -1366,461 +1366,461 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3805</v>
+        <v>2.4157</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3342</v>
+        <v>1.3539</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5403</v>
+        <v>0.5185</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3805</v>
+        <v>2.4157</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3805</v>
+        <v>2.1757</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3805</v>
+        <v>2.1757</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3805</v>
+        <v>2.1757</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K21" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3805</v>
+        <v>2.4157</v>
       </c>
       <c r="N21" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2031</v>
+        <v>2.3805</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2347</v>
+        <v>1.3342</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4686</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2031</v>
+        <v>2.3805</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9631</v>
+        <v>2.3805</v>
       </c>
       <c r="G22" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9631</v>
+        <v>2.3805</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9631</v>
+        <v>2.3805</v>
       </c>
       <c r="J22" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2031</v>
+        <v>2.3805</v>
       </c>
       <c r="N22" t="n">
-        <v>185</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9209</v>
+        <v>2.2629</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0766</v>
+        <v>1.2683</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3546</v>
+        <v>0.4576</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9209</v>
+        <v>2.2629</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6577</v>
+        <v>2.9682</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2632</v>
+        <v>-0.7053</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6577</v>
+        <v>2.9682</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6669</v>
+        <v>2.9682</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2632</v>
+        <v>-0.7053</v>
       </c>
       <c r="K23" t="n">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9301</v>
+        <v>2.2629</v>
       </c>
       <c r="N23" t="n">
-        <v>478</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8274</v>
+        <v>1.9135</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0242</v>
+        <v>1.0724</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3169</v>
+        <v>0.3184</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8274</v>
+        <v>1.9135</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8274</v>
+        <v>0.6503</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.2632</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8274</v>
+        <v>0.6503</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8274</v>
+        <v>0.6669</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.2632</v>
       </c>
       <c r="K24" t="n">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8274</v>
+        <v>1.9301</v>
       </c>
       <c r="N24" t="n">
-        <v>184</v>
+        <v>478</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9424</v>
+        <v>1.0242</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2579</v>
+        <v>0.2841</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6814</v>
+        <v>1.8274</v>
       </c>
       <c r="N25" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6437</v>
+        <v>1.81</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9212</v>
+        <v>1.0144</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2427</v>
+        <v>0.2772</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6437</v>
+        <v>1.81</v>
       </c>
       <c r="F26" t="n">
-        <v>2.349</v>
+        <v>2.1455</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7053</v>
+        <v>-0.3355</v>
       </c>
       <c r="H26" t="n">
-        <v>2.349</v>
+        <v>2.1455</v>
       </c>
       <c r="I26" t="n">
-        <v>2.349</v>
+        <v>2.1455</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7053</v>
+        <v>-0.3355</v>
       </c>
       <c r="K26" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6437</v>
+        <v>1.81</v>
       </c>
       <c r="N26" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3828</v>
+        <v>1.7683</v>
       </c>
       <c r="C27" t="n">
-        <v>0.775</v>
+        <v>0.9911</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1373</v>
+        <v>0.2606</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3828</v>
+        <v>1.7683</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.211</v>
+        <v>1.7683</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5938</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.211</v>
+        <v>1.7683</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.214</v>
+        <v>1.7683</v>
       </c>
       <c r="J27" t="n">
-        <v>1.5938</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>273</v>
+        <v>143</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3798</v>
+        <v>1.7683</v>
       </c>
       <c r="N27" t="n">
-        <v>382</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3071</v>
+        <v>1.3851</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7326</v>
+        <v>0.7763</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1067</v>
+        <v>0.1079</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3071</v>
+        <v>1.3851</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6426</v>
+        <v>-0.2087</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3355</v>
+        <v>1.5938</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6426</v>
+        <v>-0.2087</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6426</v>
+        <v>-0.214</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3355</v>
+        <v>1.5938</v>
       </c>
       <c r="K28" t="n">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="L28" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3071</v>
+        <v>1.3798</v>
       </c>
       <c r="N28" t="n">
-        <v>185</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1958</v>
+        <v>1.3635</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6702</v>
+        <v>0.7642</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0617</v>
+        <v>0.0993</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1958</v>
+        <v>1.3635</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6946</v>
+        <v>1.3635</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4988</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6946</v>
+        <v>1.3635</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3735</v>
+        <v>1.3635</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4988</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="L29" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8746999999999999</v>
+        <v>1.3635</v>
       </c>
       <c r="N29" t="n">
-        <v>208</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1532</v>
+        <v>1.1958</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6463</v>
+        <v>0.6702</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0445</v>
+        <v>0.0325</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1532</v>
+        <v>1.1958</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1532</v>
+        <v>1.6946</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4988</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1532</v>
+        <v>1.6946</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1532</v>
+        <v>1.3735</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4988</v>
       </c>
       <c r="K30" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1532</v>
+        <v>0.8746999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31">
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0935</v>
+        <v>1.0907</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6129</v>
+        <v>0.6113</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0204</v>
+        <v>-0.0094</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0935</v>
+        <v>1.0907</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2522</v>
+        <v>0.2494</v>
       </c>
       <c r="G31" t="n">
         <v>0.8413</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2522</v>
+        <v>0.2494</v>
       </c>
       <c r="I31" t="n">
         <v>0.2557</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4387</v>
+        <v>0.5703</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1051</v>
+        <v>-0.0385</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="N32" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4073</v>
+        <v>0.4387</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1278</v>
+        <v>-0.132</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7267</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34">
@@ -1974,7 +1974,7 @@
         <v>0.3598</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.162</v>
+        <v>-0.1882</v>
       </c>
       <c r="E34" t="n">
         <v>0.6419</v>
@@ -2010,354 +2010,354 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5391</v>
+        <v>0.6362</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3021</v>
+        <v>0.3566</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2036</v>
+        <v>-0.1904</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5391</v>
+        <v>0.6362</v>
       </c>
       <c r="F35" t="n">
-        <v>0.501</v>
+        <v>1.2892</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0381</v>
+        <v>-0.653</v>
       </c>
       <c r="H35" t="n">
-        <v>0.501</v>
+        <v>1.2892</v>
       </c>
       <c r="I35" t="n">
-        <v>0.501</v>
+        <v>1.2892</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0381</v>
+        <v>-0.653</v>
       </c>
       <c r="K35" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="L35" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5391</v>
+        <v>0.6361999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5362</v>
+        <v>0.5391</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3005</v>
+        <v>0.3021</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2047</v>
+        <v>-0.2291</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5362</v>
+        <v>0.5391</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5362</v>
+        <v>0.501</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.0381</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5362</v>
+        <v>0.501</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5362</v>
+        <v>0.501</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.0381</v>
       </c>
       <c r="K36" t="n">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5362</v>
+        <v>0.5391</v>
       </c>
       <c r="N36" t="n">
-        <v>83</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3001</v>
+        <v>0.3005</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.205</v>
+        <v>-0.2303</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="N37" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4608</v>
+        <v>0.5355</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2583</v>
+        <v>0.3001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2352</v>
+        <v>-0.2306</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4608</v>
+        <v>0.5355</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6484</v>
+        <v>0.5355</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1876</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6484</v>
+        <v>0.5355</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6575</v>
+        <v>0.5355</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1876</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>234</v>
+        <v>104</v>
       </c>
       <c r="L38" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4699</v>
+        <v>0.5355</v>
       </c>
       <c r="N38" t="n">
-        <v>478</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4193</v>
+        <v>0.4536</v>
       </c>
       <c r="C39" t="n">
-        <v>0.235</v>
+        <v>0.2542</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.252</v>
+        <v>-0.2632</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4193</v>
+        <v>0.4536</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4193</v>
+        <v>0.6412</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1876</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4193</v>
+        <v>0.6412</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4193</v>
+        <v>0.6575</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1876</v>
       </c>
       <c r="K39" t="n">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4193</v>
+        <v>0.4699</v>
       </c>
       <c r="N39" t="n">
-        <v>112</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2342</v>
+        <v>0.235</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2525</v>
+        <v>-0.2769</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4179</v>
+        <v>0.4193</v>
       </c>
       <c r="N40" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1759</v>
+        <v>0.2342</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2946</v>
+        <v>-0.2774</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3138</v>
+        <v>0.4179</v>
       </c>
       <c r="N41" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1407</v>
+        <v>0.1759</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3199</v>
+        <v>-0.3189</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2511</v>
+        <v>0.3138</v>
       </c>
       <c r="N42" t="n">
         <v>112</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1266</v>
+        <v>0.1407</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3301</v>
+        <v>-0.3439</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2259</v>
+        <v>0.2511</v>
       </c>
       <c r="N43" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1923</v>
+        <v>0.2259</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1078</v>
+        <v>0.1266</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3437</v>
+        <v>-0.3539</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1923</v>
+        <v>0.2259</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.2259</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.653</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.2259</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.2259</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.653</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="L44" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1923</v>
+        <v>0.2259</v>
       </c>
       <c r="N44" t="n">
-        <v>194</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1803</v>
+        <v>0.1921</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1011</v>
+        <v>0.1077</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3485</v>
+        <v>-0.3674</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1803</v>
+        <v>0.1921</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.0583</v>
+        <v>-1.0465</v>
       </c>
       <c r="G45" t="n">
         <v>1.2386</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.0583</v>
+        <v>-1.0465</v>
       </c>
       <c r="I45" t="n">
         <v>-1.0731</v>
@@ -2526,7 +2526,7 @@
         <v>0.0985</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3503</v>
+        <v>-0.3739</v>
       </c>
       <c r="E46" t="n">
         <v>0.1758</v>
@@ -2572,7 +2572,7 @@
         <v>0.0361</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3953</v>
+        <v>-0.4182</v>
       </c>
       <c r="E47" t="n">
         <v>0.0645</v>
@@ -2618,7 +2618,7 @@
         <v>0.0053</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4176</v>
+        <v>-0.4402</v>
       </c>
       <c r="E48" t="n">
         <v>0.0094</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0208</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4363</v>
+        <v>-0.4587</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0371</v>
@@ -2710,7 +2710,7 @@
         <v>-0.1212</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5087</v>
+        <v>-0.53</v>
       </c>
       <c r="E50" t="n">
         <v>-0.2162</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1248</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5113</v>
+        <v>-0.5326</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2227</v>
@@ -2802,7 +2802,7 @@
         <v>-0.176</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5482</v>
+        <v>-0.569</v>
       </c>
       <c r="E52" t="n">
         <v>-0.314</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1986</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5645</v>
+        <v>-0.5851</v>
       </c>
       <c r="E53" t="n">
         <v>-0.3544</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2255</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5839</v>
+        <v>-0.6042</v>
       </c>
       <c r="E54" t="n">
         <v>-0.4024</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2664</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.6333</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4753</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2765</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6207</v>
+        <v>-0.6405</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4934</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2861</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6276</v>
+        <v>-0.6473</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5104</v>
@@ -3078,7 +3078,7 @@
         <v>-0.329</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6585</v>
+        <v>-0.6778</v>
       </c>
       <c r="E58" t="n">
         <v>-0.587</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3557</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6778</v>
+        <v>-0.6968</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6347</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4124</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7186</v>
+        <v>-0.7371</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7358</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4411</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7393</v>
+        <v>-0.7575</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7871</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4933</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7769</v>
+        <v>-0.7946</v>
       </c>
       <c r="E62" t="n">
         <v>-0.8802</v>
@@ -3308,7 +3308,7 @@
         <v>-0.5427</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8125</v>
+        <v>-0.8297</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9683</v>
@@ -3354,7 +3354,7 @@
         <v>-0.6024</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8556</v>
+        <v>-0.8722</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0749</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HSK</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.0831</v>
+        <v>-1.082</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.607</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8589</v>
+        <v>-0.875</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.0831</v>
+        <v>-1.082</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.0831</v>
+        <v>-1.082</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.0831</v>
+        <v>-1.082</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0831</v>
+        <v>-1.1003</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.0831</v>
+        <v>-1.1003</v>
       </c>
       <c r="N65" t="n">
-        <v>76</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>HSK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0901</v>
+        <v>-1.0831</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.611</v>
+        <v>-0.607</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8617</v>
+        <v>-0.8754</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0901</v>
+        <v>-1.0831</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.0901</v>
+        <v>-1.0831</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.0901</v>
+        <v>-1.0831</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.1003</v>
+        <v>-1.0831</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>224</v>
+        <v>76</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.1003</v>
+        <v>-1.0831</v>
       </c>
       <c r="N66" t="n">
-        <v>224</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -3492,7 +3492,7 @@
         <v>-0.6412</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1441</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6988</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9251</v>
+        <v>-0.9407</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2469</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7392</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9542</v>
+        <v>-0.9694</v>
       </c>
       <c r="E69" t="n">
         <v>-1.319</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7747000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9798</v>
+        <v>-0.9946</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3823</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7868000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9885</v>
+        <v>-1.0032</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4039</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8773</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0537</v>
+        <v>-1.0675</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5653</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8817</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0569</v>
+        <v>-1.0707</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5732</v>
@@ -3814,7 +3814,7 @@
         <v>-0.996</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1393</v>
+        <v>-1.1519</v>
       </c>
       <c r="E74" t="n">
         <v>-1.7772</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0243</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1597</v>
+        <v>-1.1721</v>
       </c>
       <c r="E75" t="n">
         <v>-1.8277</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8646</v>
+        <v>-1.8507</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.045</v>
+        <v>-1.0372</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1746</v>
+        <v>-1.1812</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8646</v>
+        <v>-1.8507</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8646</v>
+        <v>-1.8507</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8646</v>
+        <v>-1.8507</v>
       </c>
       <c r="I76" t="n">
         <v>-1.882</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1975</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2845</v>
+        <v>-1.2951</v>
       </c>
       <c r="E77" t="n">
         <v>-2.1366</v>
@@ -3998,7 +3998,7 @@
         <v>-1.7225</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6629</v>
+        <v>-1.6683</v>
       </c>
       <c r="E78" t="n">
         <v>-3.0733</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.2809</v>
+        <v>-3.2615</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.8388</v>
+        <v>-1.8279</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7468</v>
+        <v>-1.7433</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.2809</v>
+        <v>-3.2615</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.744</v>
+        <v>-1.7246</v>
       </c>
       <c r="G79" t="n">
         <v>-1.5369</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.744</v>
+        <v>-1.7246</v>
       </c>
       <c r="I79" t="n">
         <v>-1.7685</v>
@@ -4090,7 +4090,7 @@
         <v>-1.8614</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7631</v>
+        <v>-1.7671</v>
       </c>
       <c r="E80" t="n">
         <v>-3.3212</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.0534</v>
+        <v>-4.0162</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.2718</v>
+        <v>-2.2509</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0588</v>
+        <v>-2.044</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.0534</v>
+        <v>-4.0162</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.3353</v>
+        <v>-3.2981</v>
       </c>
       <c r="G81" t="n">
         <v>-0.7181</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.3353</v>
+        <v>-3.2981</v>
       </c>
       <c r="I81" t="n">
         <v>-3.3821</v>
